--- a/InputFiles/CDS/Single Filter Testcases/TC07_CDS_phs002529_LibrarySource_Viral RNA.xlsx
+++ b/InputFiles/CDS/Single Filter Testcases/TC07_CDS_phs002529_LibrarySource_Viral RNA.xlsx
@@ -1,268 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kallakuriv2\Automation\sowjanya0925\Commons_Automation\InputFiles\CDS\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEAD96D-ECF6-4B65-8EFF-65CCBC941193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>WebExcel</t>
-  </si>
-  <si>
-    <t>StatQuery</t>
-  </si>
-  <si>
-    <t>TabName</t>
-  </si>
-  <si>
-    <t>SamplesTab</t>
-  </si>
-  <si>
-    <t>FilesTab</t>
-  </si>
-  <si>
-    <t>ParticipantsTab</t>
-  </si>
-  <si>
-    <t>TabQuery</t>
-  </si>
-  <si>
-    <t>TsvExcel</t>
-  </si>
-  <si>
-    <t>TC07_CDS_phs002529_LibrarySource_Viral RNA_TSVData.xlsx</t>
-  </si>
-  <si>
-    <t>TC07_CDS_phs002529_LibrarySource_Viral RNA_WebData.xlsx</t>
-  </si>
-  <si>
-    <t>SELECT
-    COUNT(DISTINCT s.study_name) AS "Studies",
-    COUNT(DISTINCT sp.participant_id) AS "Participants",
-    COUNT(DISTINCT smp.sample_id) AS "Samples",
-    COUNT(DISTINCT f.file_id) AS "Files"
-FROM 
-    df_participant sp
-JOIN 
-    df_study s ON sp."study.phs_accession" = s.phs_accession
-JOIN 
-    df_sample smp ON smp."participant.study_participant_id" = sp.study_participant_id
-JOIN 
-    df_program p ON p.program_acronym = s."program.program_acronym"
-JOIN 
-    df_file f ON f."sample.sample_id" = smp.sample_id
-JOIN 
-    df_diagnosis d ON d."participant.study_participant_id" = sp.study_participant_id
-JOIN 
-    df_genomic_info gi ON gi."file.file_id" = f.file_id
-WHERE 
-    s.phs_accession = 'phs002529' AND gi.library_source = 'Viral RNA';</t>
-  </si>
-  <si>
-    <t>WITH Distinct_Samples AS (
-    SELECT DISTINCT
-        sp.participant_id,
-        sp.study_participant_id,
-        s.study_name,
-        s.phs_accession,
-        sp.gender,
-        smp.sample_id
-    FROM 
-        df_participant sp
-    JOIN 
-        df_study s ON sp."study.phs_accession" = s.phs_accession
-    JOIN 
-        df_sample smp ON smp."participant.study_participant_id" = sp.study_participant_id
-    JOIN
-        df_diagnosis d ON d."participant.study_participant_id" = sp.study_participant_id
-    JOIN
-        df_program p ON p.program_acronym = s."program.program_acronym"
-    JOIN
-        df_file f1 ON f1."sample.sample_id" = smp.sample_id
-    JOIN
-        df_genomic_info gi ON gi."file.file_id" = f1.file_id
-    WHERE 
-        s.phs_accession = 'phs002529' AND gi.library_source = 'Viral RNA'
-),
-Sample_Limit AS (
-    SELECT
-        participant_id,
-        study_participant_id,
-        study_name,
-        phs_accession,
-        gender,
-        sample_id,
-        ROW_NUMBER() OVER (PARTITION BY study_participant_id ORDER BY sample_id) as rn
-    FROM 
-        Distinct_Samples
-)
-SELECT
-    participant_id AS "Participant ID", 
-    study_name AS "Study Name",
-    phs_accession AS Accession,
-    gender AS Gender,
-    GROUP_CONCAT(
-        CASE 
-            WHEN rn &lt;= 5 THEN sample_id 
-        END, ', '
-    ) ||
-    CASE 
-        WHEN MAX(rn) &gt; 5 THEN ', ...' 
-        ELSE '' 
-    END AS Samples
-FROM 
-    Sample_Limit
-GROUP BY
-    participant_id, 
-    study_name,
-    phs_accession,
-    gender
-LIMIT 100;</t>
-  </si>
-  <si>
-    <t>SELECT
-    f1.file_name AS "File Name",
-    s.study_name AS "Study Name",
-    s.phs_accession AS "Accession",
-    sp.participant_id AS "Participant Id",
-    COALESCE((
-        SELECT
-            REPLACE(GROUP_CONCAT(CASE WHEN rn &lt;= 5 THEN smp.sample_id ELSE NULL END, ', '), ', , ', ', ') ||
-            CASE WHEN MAX(rn) &gt; 5 THEN ', ...' ELSE '' END
-        FROM (
-            SELECT
-                smp.sample_id,
-                ROW_NUMBER() OVER (ORDER BY smp.sample_id) AS rn
-            FROM df_sample smp
-            WHERE smp."participant.study_participant_id" = sp.study_participant_id
-        ) smp
-    ), '') AS "Sample Id",
-    f1.file_type AS "File Type",
-    gi.library_strategy AS "Library Strategy"
-FROM 
-    df_study s
-INNER JOIN 
-    df_participant sp ON sp."study.phs_accession" = s.phs_accession
-INNER JOIN  
-    df_sample smp ON smp."participant.study_participant_id" = sp.study_participant_id
-INNER JOIN 
-    df_file f1 ON f1."sample.sample_id" = smp.sample_id
-INNER JOIN
-    df_genomic_info gi ON gi."file.file_id" = f1.file_id
-INNER JOIN
-    df_diagnosis d ON d."participant.study_participant_id" = sp.study_participant_id
-INNER JOIN
-    df_program p ON p.program_acronym = s."program.program_acronym"
-WHERE 
- s.phs_accession = 'phs002529' AND gi.library_source = 'Viral RNA'
-GROUP BY
-    f1.file_name,
-    s.study_name,
-    s.phs_accession,
-    sp.participant_id,
-    f1.file_type,
-    gi.library_strategy
-ORDER BY 
-    f1.file_name ASC
-LIMIT 100;</t>
-  </si>
-  <si>
-    <t>SELECT
-    DISTINCT (smp.sample_id) AS "Sample ID",
-    sp.participant_id AS "Participant ID", 
-    s.study_name AS "Study Name",
-    s.phs_accession AS Accession
-FROM 
-    df_participant sp
-JOIN 
-    df_study s ON sp."study.phs_accession" = s.phs_accession
-JOIN 
-    df_sample smp ON smp."participant.study_participant_id" = sp.study_participant_id
-JOIN
-    df_diagnosis d ON d."participant.study_participant_id" = sp.study_participant_id
-JOIN
-    df_program p ON p.program_acronym = s."program.program_acronym"
-JOIN
-    df_file f1 ON f1."sample.sample_id" = smp.sample_id
-JOIN
-    df_genomic_info gi ON gi."file.file_id" = f1.file_id
-WHERE 
-    s.phs_accession = 'phs002529' AND gi.library_source = 'Viral RNA'
-ORDER BY 
-    smp.sample_id ASC
-LIMIT 100;</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -282,31 +74,90 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{7EA68BB1-159D-4F44-96A3-D0B7FBE8815D}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -606,78 +457,164 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C538400-E87C-4027-A918-A51DB80B3430}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="75.85546875" customWidth="1"/>
-    <col min="4" max="4" width="70.140625" customWidth="1"/>
-    <col min="5" max="5" width="63.42578125" bestFit="1" customWidth="1"/>
+    <col width="12.140625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="75.85546875" customWidth="1" min="2" max="3"/>
+    <col width="70.140625" customWidth="1" min="4" max="4"/>
+    <col width="63.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TabName</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TabQuery</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>StatQuery</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TsvExcel</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>WebExcel</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+    <row r="2" ht="409.5" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ParticipantsTab</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MATCH (gi:genomic_info)-[:of_file]-&gt;(f:file)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+WHERE s.phs_accession = "phs002529"
+  AND gi.library_source = "Viral RNA"
+WITH DISTINCT p, s
+OPTIONAL MATCH (samp_all:sample)-[:of_participant]-&gt;(p)
+WITH p, s, samp_all
+ORDER BY samp_all.sample_id ASC
+WITH p, s, [x IN collect(samp_all.sample_id) WHERE x IS NOT NULL] AS sample_ids
+WITH p, s, sample_ids,
+  CASE
+    WHEN size(sample_ids) &gt; 5
+    THEN reduce(acc = "", id IN sample_ids[0..5] | CASE WHEN acc = "" THEN id ELSE acc + ", " + id END) + ", ..."
+    ELSE reduce(acc = "", id IN sample_ids | CASE WHEN acc = "" THEN id ELSE acc + ", " + id END)
+  END AS samples
+RETURN
+  p.participant_id AS participant_id,
+  s.study_name AS study_name,
+  s.phs_accession AS accession,
+  p.sex AS sex,
+  samples
+ORDER BY p.participant_id ASC
+LIMIT 100
+</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MATCH (gi:genomic_info)-[:of_file]-&gt;(f:file)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+WHERE s.phs_accession = "phs002529"
+  AND gi.library_source = "Viral RNA"
+OPTIONAL MATCH (f)-[:from_sample]-&gt;(samp:sample)
+RETURN
+  count(DISTINCT s) AS Studies,
+  count(DISTINCT p) AS Participants,
+  count(DISTINCT samp) AS Samples,
+  count(DISTINCT f) AS Files
+</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TC07_CDS_phs002529_LibrarySource_Viral RNA_TSVData.xlsx</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TC07_CDS_phs002529_LibrarySource_Viral RNA_WebData.xlsx</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2"/>
+    <row r="3" ht="409.5" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SamplesTab</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MATCH (gi:genomic_info)-[:of_file]-&gt;(f:file)-[:from_sample]-&gt;(samp:sample)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+WHERE s.phs_accession = "phs002529"
+  AND gi.library_source = "Viral RNA"
+RETURN DISTINCT
+  s.study_acronym AS study_name,
+  s.phs_accession AS accession,
+  samp.sample_id AS sample_id,
+  COALESCE(samp.sample_name, samp.sample_id) AS sample_name,
+  COALESCE(samp.Organization_Name, "Not specified in data") AS organization_name
+ORDER BY samp.sample_id ASC
+LIMIT 100
+</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
     </row>
-    <row r="4" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2"/>
+    <row r="4" ht="409.5" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FilesTab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MATCH (gi:genomic_info)-[:of_file]-&gt;(f:file)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+WHERE s.phs_accession = "phs002529"
+  AND gi.library_source = "Viral RNA"
+OPTIONAL MATCH (f)-[:from_sample]-&gt;(samp:sample)
+RETURN DISTINCT
+  s.study_name AS study_name,
+  s.phs_accession AS accession,
+  f.file_name AS file_name,
+  f.file_id AS file_id,
+  f.file_type AS file_type,
+  COALESCE(samp.sample_id, "Not Applicable") AS sample_id
+ORDER BY f.file_name ASC
+LIMIT 100
+</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+    <row r="5">
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="1" t="n"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C6" s="1"/>
+    <row r="6">
+      <c r="C6" s="1" t="n"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>